--- a/CO2xNxPhrag/Porewater/1-Sulfide/2026/Datasheets/2026July_LTREB_H2S_Datasheets.xlsx
+++ b/CO2xNxPhrag/Porewater/1-Sulfide/2026/Datasheets/2026July_LTREB_H2S_Datasheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\GlobalChangeEco\Porewater_R scripts &amp; Data\Data\Sulfide Microplate\LTREB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/GENX/Porewater/1-Sulfide/2026/Datasheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4499AA84-BEDA-4AA7-992D-9710CA7EE46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{4499AA84-BEDA-4AA7-992D-9710CA7EE46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C50CD9CF-EF62-43CE-8425-514EA23870C1}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="1320" windowWidth="17895" windowHeight="12600" firstSheet="8" activeTab="13" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
+    <workbookView xWindow="0" yWindow="1110" windowWidth="16590" windowHeight="11295" firstSheet="9" activeTab="14" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
   </bookViews>
   <sheets>
     <sheet name="STD 1" sheetId="1" r:id="rId1"/>
@@ -5848,13 +5848,13 @@
         <v>50</v>
       </c>
       <c r="H18" s="4">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="I18" s="4">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="J18" s="4">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>

--- a/CO2xNxPhrag/Porewater/1-Sulfide/2026/Datasheets/2026July_LTREB_H2S_Datasheets.xlsx
+++ b/CO2xNxPhrag/Porewater/1-Sulfide/2026/Datasheets/2026July_LTREB_H2S_Datasheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/GENX/Porewater/1-Sulfide/2026/Datasheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/CO2xN/Porewater/1-Sulfide/2026/Datasheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{4499AA84-BEDA-4AA7-992D-9710CA7EE46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C50CD9CF-EF62-43CE-8425-514EA23870C1}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{4499AA84-BEDA-4AA7-992D-9710CA7EE46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05DA49CC-AEBE-4733-A65E-72F592A1AE35}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1110" windowWidth="16590" windowHeight="11295" firstSheet="9" activeTab="14" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
+    <workbookView xWindow="19635" yWindow="780" windowWidth="22515" windowHeight="13380" firstSheet="8" activeTab="17" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
   </bookViews>
   <sheets>
     <sheet name="STD 1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,10 @@
     <sheet name="Plate 10" sheetId="12" r:id="rId13"/>
     <sheet name="STD 4" sheetId="15" r:id="rId14"/>
     <sheet name="Plate 11" sheetId="13" r:id="rId15"/>
-    <sheet name="QAQC" sheetId="2" r:id="rId16"/>
+    <sheet name="STD 5" sheetId="17" r:id="rId16"/>
+    <sheet name="Rerun1" sheetId="18" r:id="rId17"/>
+    <sheet name="Rerun2" sheetId="19" r:id="rId18"/>
+    <sheet name="QAQC" sheetId="2" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -51,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="250">
   <si>
     <t>A</t>
   </si>
@@ -789,6 +792,18 @@
   </si>
   <si>
     <t>Melanie</t>
+  </si>
+  <si>
+    <t>Ch10-70</t>
+  </si>
+  <si>
+    <t>Ch6-80 Dup</t>
+  </si>
+  <si>
+    <t>310-40</t>
+  </si>
+  <si>
+    <t>462-120</t>
   </si>
 </sst>
 </file>
@@ -5914,6 +5929,1556 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975BED34-0A32-44EE-911B-780801835F60}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DE7FC4-87BD-4158-B952-4FEA0384955E}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4">
+        <v>50</v>
+      </c>
+      <c r="G12" s="4">
+        <v>50</v>
+      </c>
+      <c r="H12" s="4">
+        <v>250</v>
+      </c>
+      <c r="I12" s="4">
+        <v>250</v>
+      </c>
+      <c r="J12" s="4">
+        <v>250</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>50</v>
+      </c>
+      <c r="F13" s="4">
+        <v>50</v>
+      </c>
+      <c r="G13" s="4">
+        <v>50</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>50</v>
+      </c>
+      <c r="F14" s="4">
+        <v>50</v>
+      </c>
+      <c r="G14" s="4">
+        <v>50</v>
+      </c>
+      <c r="H14" s="4">
+        <v>250</v>
+      </c>
+      <c r="I14" s="4">
+        <v>250</v>
+      </c>
+      <c r="J14" s="4">
+        <v>250</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4">
+        <v>25</v>
+      </c>
+      <c r="G15" s="4">
+        <v>25</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>250</v>
+      </c>
+      <c r="F16" s="4">
+        <v>250</v>
+      </c>
+      <c r="G16" s="4">
+        <v>250</v>
+      </c>
+      <c r="H16" s="4">
+        <v>100</v>
+      </c>
+      <c r="I16" s="4">
+        <v>100</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>250</v>
+      </c>
+      <c r="F17" s="4">
+        <v>250</v>
+      </c>
+      <c r="G17" s="4">
+        <v>250</v>
+      </c>
+      <c r="H17" s="4">
+        <v>100</v>
+      </c>
+      <c r="I17" s="4">
+        <v>100</v>
+      </c>
+      <c r="J17" s="4">
+        <v>100</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>250</v>
+      </c>
+      <c r="F18" s="4">
+        <v>250</v>
+      </c>
+      <c r="G18" s="4">
+        <v>250</v>
+      </c>
+      <c r="H18" s="4">
+        <v>250</v>
+      </c>
+      <c r="I18" s="4">
+        <v>250</v>
+      </c>
+      <c r="J18" s="4">
+        <v>250</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4">
+        <v>50</v>
+      </c>
+      <c r="C19" s="4">
+        <v>50</v>
+      </c>
+      <c r="D19" s="4">
+        <v>50</v>
+      </c>
+      <c r="E19" s="4">
+        <v>250</v>
+      </c>
+      <c r="F19" s="4">
+        <v>250</v>
+      </c>
+      <c r="G19" s="4">
+        <v>250</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285B18F9-3E5B-4EB2-BE39-24934CBA58D0}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4">
+        <v>25</v>
+      </c>
+      <c r="L14" s="4">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74720A33-EA02-4F3B-99BC-21807D7702E9}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
